--- a/histograms/histogram_frac_f_valence_electrons.xlsx
+++ b/histograms/histogram_frac_f_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.01029411764705883</v>
       </c>
       <c r="B2" t="n">
-        <v>18241</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.03088235294117648</v>
       </c>
       <c r="B3" t="n">
-        <v>242</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.05147058823529413</v>
       </c>
       <c r="B4" t="n">
-        <v>1865</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.07205882352941177</v>
       </c>
       <c r="B5" t="n">
-        <v>1149</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.09264705882352943</v>
       </c>
       <c r="B6" t="n">
-        <v>282</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.1132352941176471</v>
       </c>
       <c r="B7" t="n">
-        <v>410</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.1338235294117647</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.1544117647058824</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -525,7 +525,7 @@
         <v>0.2161764705882353</v>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>0.236764705882353</v>
       </c>
       <c r="B13" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0.2573529411764706</v>
       </c>
       <c r="B14" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>0.2779411764705882</v>
       </c>
       <c r="B15" t="n">
-        <v>1472</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>0.2985294117647059</v>
       </c>
       <c r="B16" t="n">
-        <v>296</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0.3191176470588236</v>
       </c>
       <c r="B17" t="n">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0.3397058823529412</v>
       </c>
       <c r="B18" t="n">
-        <v>1097</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0.3602941176470589</v>
       </c>
       <c r="B19" t="n">
-        <v>696</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>0.3808823529411766</v>
       </c>
       <c r="B20" t="n">
-        <v>139</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
